--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/phi-4/metrics_default_vs_aae.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/phi-4/metrics_default_vs_aae.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.9108910891089109</v>
+        <v>0.9191919191919192</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.7535211267605634</v>
+        <v>0.7394366197183099</v>
       </c>
       <c r="D2">
-        <v>0.2755905511811024</v>
+        <v>0.2890625</v>
       </c>
       <c r="E2">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
